--- a/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bertrand est près de la fenêtre. Papa est avec lui. Une petite plante a soif. Ses feuilles sont molles. Papa dit : elle a besoin d'eau. Elle a besoin de lumière. Bertrand prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la vitre. La lumière arrive. Bertrand touche une feuille. C'est doux. Papa dit : on arrose avec un adulte. L'adulte est là. Bertrand range l'arrosoir.</t>
+          <t>Bertrand est près de la fenêtre. Papa est avec lui. Une petite plante a soif. Ses feuilles sont molles. Elle a besoin d'eau. Elle a besoin de lumière. Bertrand prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la vitre. La lumière arrive. Bertrand touche une feuille. C'est doux. On arrose avec un adulte. L'adulte est là. Bertrand range l'arrosoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand est près de la fenêtre. Papa est avec lui. Une petite plante a soif. Ses feuilles sont molles.
+papa|Elle a besoin d'eau. Elle a besoin de lumière.
+narrateur|Bertrand prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la vitre. La lumière arrive. Bertrand touche une feuille. C'est doux.
+papa|On arrose avec un adulte. L'adulte est là.
+narrateur|Bertrand range l'arrosoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a soif. Que fait Bertrand avec papa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bertrand essuie une goutte. La plante tient droit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Bertrand range l'arrosoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|La plante a soif. Que fait Bertrand avec papa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Bertrand a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Bertrand essuie une goutte. La plante tient droit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bertrand arrose la plante</t>
+          <t>Le tuteur de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut que la tomate tienne droit. Le tuteur penche. Ils le redressent. Ils arrosent. La tige tient au soleil.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bertrand est près de la fenêtre. Papa est avec lui. Une petite plante a soif. Ses feuilles sont molles. Elle a besoin d'eau. Elle a besoin de lumière. Bertrand prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la vitre. La lumière arrive. Bertrand touche une feuille. C'est doux. On arrose avec un adulte. L'adulte est là. Bertrand range l'arrosoir.</t>
+          <t>Un fil de soleil coupe le rebord. Un pot de tomate est là. La terre est un peu claire. Un tuteur en bois penche. La tige penche avec lui. Une petite tomate verte tient encore. Papa pose un arrosoir près du mur. L'arrosoir est rouge et lisse. Tu vois la tomate, Nino ? Elle penche, papa. Je veux qu'elle tienne droit. Le tuteur penche trop. En ce moment, Nino touche le bois. Le bois est sec. On le redresse ? Oui, doucement. Nino tient le tuteur. Papa tient le pot. Ils poussent tout doux. Le tuteur se redresse. La tige aussi. Elle est droite. La terre est sèche, tu vois ? Elle a besoin d'eau. Elle a besoin de lumière. On arrose ? Oui, avec moi. Nino prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Une goutte file sur le rebord. Nino l'essuie. Elle boit. Oui. Papa pousse le pot vers le soleil. Le fil de soleil touche les feuilles. Elle a de la lumière. Oui, Nino. Une feuille se redresse un peu. Nino la touche, tout doux. Elle est douce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bertrand est près de la fenêtre. Papa est avec lui. Une petite plante a soif. Ses feuilles sont molles. Papa dit : elle a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Bertrand prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la vitre. La lumière arrive. Bertrand touche une feuille. C'est doux. Papa dit : on arrose avec un adulte. L'adulte est là. Bertrand range l'arrosoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un fil de soleil coupe le rebord. Un pot de tomate est là. La terre est un peu claire. Un tuteur en bois penche. La tige penche avec lui. Une petite tomate verte tient encore. Papa pose un arrosoir près du mur. L'arrosoir est rouge et lisse. Tu vois la tomate, Nino ? Elle penche, papa. Je veux qu'elle tienne droit. Le tuteur penche trop. En ce moment, Nino touche le bois. Le bois est sec. On le redresse ? Oui, doucement. Nino tient le tuteur. Papa tient le pot. Ils poussent tout doux. Le tuteur se redresse. La tige aussi. Elle est droite. La terre est sèche, tu vois ? Elle a besoin d'eau. Elle a besoin de lumière. On arrose ? Oui, avec moi. Nino prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Une goutte file sur le rebord. Nino l'essuie. Elle boit. Oui. Papa pousse le pot vers le soleil. Le fil de soleil touche les feuilles. Elle a de la lumière. Oui, Nino. Une feuille se redresse un peu. Nino la touche, tout doux. Elle est douce.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand est près de la fenêtre. Papa est avec lui. Une petite plante a soif. Ses feuilles sont molles.
-papa|Elle a besoin d'eau. Elle a besoin de lumière.
-narrateur|Bertrand prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la vitre. La lumière arrive. Bertrand touche une feuille. C'est doux.
-papa|On arrose avec un adulte. L'adulte est là.
-narrateur|Bertrand range l'arrosoir.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un fil de soleil coupe le rebord.
+narrateur|Un pot de tomate est là.
+narrateur|La terre est un peu claire.
+narrateur|Un tuteur en bois penche.
+narrateur|La tige penche avec lui.
+narrateur|Une petite tomate verte tient encore.
+narrateur|Papa pose un arrosoir près du mur.
+narrateur|L'arrosoir est rouge et lisse.
+papa|Tu vois la tomate, Nino ?
+enfant-m|Elle penche, papa.
+enfant-m|Je veux qu'elle tienne droit.
+papa|Le tuteur penche trop.
+narrateur|En ce moment, Nino touche le bois.
+narrateur|Le bois est sec.
+enfant-m|On le redresse ?
+papa|Oui, doucement.
+narrateur|Nino tient le tuteur.
+narrateur|Papa tient le pot.
+narrateur|Ils poussent tout doux.
+narrateur|Le tuteur se redresse.
+narrateur|La tige aussi.
+enfant-m|Elle est droite.
+papa|La terre est sèche, tu vois ?
+papa|Elle a besoin d'eau.
+papa|Elle a besoin de lumière.
+enfant-m|On arrose ?
+papa|Oui, avec moi.
+narrateur|Nino prend l'arrosoir avec papa.
+narrateur|Ils versent un peu d'eau.
+narrateur|La terre devient sombre.
+narrateur|Une goutte file sur le rebord.
+narrateur|Nino l'essuie.
+enfant-m|Elle boit.
+papa|Oui.
+narrateur|Papa pousse le pot vers le soleil.
+narrateur|Le fil de soleil touche les feuilles.
+enfant-m|Elle a de la lumière.
+papa|Oui, Nino.
+narrateur|Une feuille se redresse un peu.
+narrateur|Nino la touche, tout doux.
+enfant-m|Elle est douce.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1391,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La plante a soif. Que fait Bertrand avec papa ?</t>
+          <t>La tomate a soif. Que fait Nino avec papa ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La plante a soif. Que fait Bertrand avec papa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tomate a soif. Que fait Nino avec papa ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1411,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>arroser | il arrose | de l'eau | eau</t>
+          <t>arroser | de l'eau | eau | lumière | tuteur | avec papa</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils versent de l'eau. Que fait Bertrand ?</t>
+          <t>Ils versent de l'eau. Que fait Nino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1475,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1547,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La plante a soif. Que fait Bertrand avec papa ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La tomate a soif.
+narrateur|Que fait Nino avec papa ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1575,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bertrand a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
+          <t>Nino regarde encore le tuteur. Il ne penche plus. Il tient bien ? Oui, papa. Papa noue un brin de raphia. Le nœud est doux, pas serré. Pour la tige. Oui, pour qu'elle reste droite. Merci, Nino. Nino pose la main sur la terre. Elle est fraîche, maintenant. Elle a de l'eau. Et le soleil, là. La petite tomate verte brille. On range l'arrosoir ? Oui. Nino pose l'arrosoir près du mur. Une goutte tombe encore. Nino l'essuie avec le doigt. Le tuteur est droit. Oui, il tient. La petite tomate verte brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bertrand a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Papa, l'adulte, était avec lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino regarde encore le tuteur. Il ne penche plus. Il tient bien ? Oui, papa. Papa noue un brin de raphia. Le nœud est doux, pas serré. Pour la tige. Oui, pour qu'elle reste droite. Merci, Nino. Nino pose la main sur la terre. Elle est fraîche, maintenant. Elle a de l'eau. Et le soleil, là. La petite tomate verte brille. On range l'arrosoir ? Oui. Nino pose l'arrosoir près du mur. Une goutte tombe encore. Nino l'essuie avec le doigt. Le tuteur est droit. Oui, il tient. La petite tomate verte brille encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1589,14 +1636,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1719,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino regarde encore le tuteur.
+narrateur|Il ne penche plus.
+papa|Il tient bien ?
+enfant-m|Oui, papa.
+narrateur|Papa noue un brin de raphia.
+narrateur|Le nœud est doux, pas serré.
+enfant-m|Pour la tige.
+papa|Oui, pour qu'elle reste droite.
+papa|Merci, Nino.
+narrateur|Nino pose la main sur la terre.
+narrateur|Elle est fraîche, maintenant.
+enfant-m|Elle a de l'eau.
+papa|Et le soleil, là.
+narrateur|La petite tomate verte brille.
+papa|On range l'arrosoir ?
+enfant-m|Oui.
+narrateur|Nino pose l'arrosoir près du mur.
+narrateur|Une goutte tombe encore.
+narrateur|Nino l'essuie avec le doigt.
+enfant-m|Le tuteur est droit.
+papa|Oui, il tient.
+narrateur|La petite tomate verte brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bertrand essuie une goutte. La plante tient droit.</t>
+          <t>Le rebord est un peu mouillé. Nino passe le linge. Tu as fini le rebord ? Oui, papa. La tige tient droit. Le tuteur aussi. Elle va grandir ? Avec de l'eau. Avec de la lumière. Le fil de soleil reste sur les feuilles. Je la vois. Moi aussi. Nino pose le linge près du mur. Le rebord redevient sec. Elle tient droit, maintenant. Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bertrand essuie une goutte. La plante tient droit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rebord est un peu mouillé. Nino passe le linge. Tu as fini le rebord ? Oui, papa. La tige tient droit. Le tuteur aussi. Elle va grandir ? Avec de l'eau. Avec de la lumière. Le fil de soleil reste sur les feuilles. Je la vois. Moi aussi. Nino pose le linge près du mur. Le rebord redevient sec. Elle tient droit, maintenant. Oui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1761,14 +1828,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1903,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bertrand essuie une goutte. La plante tient droit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le rebord est un peu mouillé.
+narrateur|Nino passe le linge.
+papa|Tu as fini le rebord ?
+enfant-m|Oui, papa.
+narrateur|La tige tient droit.
+narrateur|Le tuteur aussi.
+enfant-m|Elle va grandir ?
+papa|Avec de l'eau.
+papa|Avec de la lumière.
+narrateur|Le fil de soleil reste sur les feuilles.
+enfant-m|Je la vois.
+papa|Moi aussi.
+narrateur|Nino pose le linge près du mur.
+narrateur|Le rebord redevient sec.
+enfant-m|Elle tient droit, maintenant.
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La tomate tient droit dans son pot. Le tuteur aussi. Oui. Le fil de soleil reste sur les feuilles. La petite tomate verte attend le jour.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tomate tient droit dans son pot. Le tuteur aussi. Oui. Le fil de soleil reste sur les feuilles. La petite tomate verte attend le jour.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2006,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2085,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La tomate tient droit dans son pot.
+enfant-m|Le tuteur aussi.
+papa|Oui.
+narrateur|Le fil de soleil reste sur les feuilles.
+narrateur|La petite tomate verte attend le jour.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-10.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bertrand, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
